--- a/dyzury.xlsx
+++ b/dyzury.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maciejnajwer/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E1CC226-89D0-AA45-9B63-213BF3ECEE1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{072A0885-17AD-F046-A3BC-ED2F7C097392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="34200" yWindow="600" windowWidth="27780" windowHeight="18800" xr2:uid="{AAF0BBCE-FED5-4D46-8711-00D9F938D315}"/>
   </bookViews>
@@ -1312,7 +1312,7 @@
         <v>43</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>42</v>
